--- a/scholarship_application_forms/044_pearls_scholarship_app--scholarship_application_forms.xlsx
+++ b/scholarship_application_forms/044_pearls_scholarship_app--scholarship_application_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,11 +437,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E67"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
+    <col width="37" customWidth="1" min="2" max="2"/>
     <col width="31" customWidth="1" min="3" max="3"/>
     <col width="47" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -543,7 +543,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>pearls_program</t>
+          <t>program</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1071,17 +1071,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>additional_information</t>
+          <t>student_citizenship</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Additional Information</t>
+          <t>Student-Citizenship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>parental_contact_address</t>
+          <t>student_country_of_origin</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Parental Contact Address</t>
+          <t>Student-Country of Origin</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -1122,12 +1122,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>school_city</t>
+          <t>student_language</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>School City</t>
+          <t>Student-Language</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1145,12 +1145,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>school_state</t>
+          <t>student_language_other</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>School State</t>
+          <t>Other (If other, specify)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1163,17 +1163,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>student_citizenship</t>
+          <t>student_lived_abroad</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Student-Citizenship</t>
+          <t>Lived Abroad</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -1191,12 +1191,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>student_country_of_origin</t>
+          <t>student_lived_abroad_country</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Student-Country of Origin</t>
+          <t>If yes, country</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1214,12 +1214,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>student_language</t>
+          <t>school_district_other</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Student-Language</t>
+          <t>School District Other</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1232,17 +1232,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>student_language_other</t>
+          <t>student_languages_spoken</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Other (If other, specify)</t>
+          <t>Student Languages Spoken</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>student_lived_abroad</t>
+          <t>additional_languages_spoken</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Lived Abroad</t>
+          <t>Additional Languages Spoken</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -1283,706 +1283,16 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>student_lived_abroad_country</t>
+          <t>student_languages_spoken_other</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>If yes, country</t>
+          <t>Other (Specify)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>school_district_other</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Other (If other, specify)</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>student_languages_spoken</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Student Languages Spoken</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>additional_languages_spoken</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Additional Languages Spoken</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>student_languages_spoken_other</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Other (Specify)</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>student_languages_spoken_other_1</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Other (Specify)</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>student_languages_spoken_other_1_other</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Other (Specify)</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>student_languages_spoken_other_2</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Other (Specify)</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>student_languages_spoken_other_2_other</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Other (Specify)</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>student_languages_spoken_other_3</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Other (Specify)</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>student_languages_spoken_other_3_other</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Other (Specify)</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>student_languages_spoken_other_4</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Other (Specify)</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>student_languages_spoken_other_4_other</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Other (Specify)</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>student_languages_spoken_other_5</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Other (Specify)</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>student_languages_spoken_other_5_other</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Other (Specify)</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>student_languages_spoken_other_6</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Other (Specify)</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>student_languages_spoken_other_6_other</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Other (Specify)</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>student_languages_spoken_other_7</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Other (Specify)</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>student_languages_spoken_other_7_other</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Other (Specify)</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>student_languages_spoken_other_8</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Other (Specify)</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>student_languages_spoken_other_8_other</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Other (Specify)</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>student_languages_spoken_other_9</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Other (Specify)</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>student_languages_spoken_other_9_other</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Other (Specify)</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>student_languages_spoken_other_10</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Other (Specify)</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>student_languages_spoken_other_10_other</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Other (Specify)</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>student_languages_spoken_other_11</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Other (Specify)</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>student_languages_spoken_other_11_other</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Other (Specify)</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>student_languages_spoken_other_12</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Other (Specify)</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>student_languages_spoken_other_12_other</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Other (Specify)</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>student_languages_spoken_other_13</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Other (Specify)</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>student_languages_spoken_other_13_other</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Other (Specify)</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1999,12 +1309,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2027,51 +1337,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>pearls_program_choices</t>
+          <t>program_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'pearls'}</t>
+          <t>pearls</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'PEARLS'}</t>
+          <t>PEARLS</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>pearls_program_choices</t>
+          <t>program_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'pearlsplus'}</t>
+          <t>pearlsplus</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'PearlsPlus'}</t>
+          <t>PearlsPlus</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>pearls_program_choices</t>
+          <t>program_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'pearlsmax'}</t>
+          <t>pearlsmax</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'PearlsMax'}</t>
+          <t>PearlsMax</t>
         </is>
       </c>
     </row>
@@ -2083,12 +1393,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'biological'}</t>
+          <t>biological</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Biological'}</t>
+          <t>Biological</t>
         </is>
       </c>
     </row>
@@ -2100,12 +1410,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'adopted'}</t>
+          <t>adopted</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Adopted'}</t>
+          <t>Adopted</t>
         </is>
       </c>
     </row>
@@ -2117,12 +1427,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'fostered'}</t>
+          <t>fostered</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Fostered'}</t>
+          <t>Fostered</t>
         </is>
       </c>
     </row>
@@ -2134,12 +1444,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'hispanic'}</t>
+          <t>hispanic</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Hispanic'}</t>
+          <t>Hispanic</t>
         </is>
       </c>
     </row>
@@ -2151,12 +1461,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'non-hispanic'}</t>
+          <t>non-hispanic</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Non-Hispanic'}</t>
+          <t>Non-Hispanic</t>
         </is>
       </c>
     </row>
@@ -2168,12 +1478,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'citizen'}</t>
+          <t>citizen</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Citizen'}</t>
+          <t>Citizen</t>
         </is>
       </c>
     </row>
@@ -2185,12 +1495,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'non-citizen'}</t>
+          <t>non-citizen</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Non-Citizen'}</t>
+          <t>Non-Citizen</t>
         </is>
       </c>
     </row>
@@ -2202,12 +1512,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -2219,12 +1529,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Spanish'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -2236,29 +1546,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>student_languages_spoken_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>{'value':_'both'}</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>{'value': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
